--- a/PC4NOOBS_Arbeitsjournal.xlsx
+++ b/PC4NOOBS_Arbeitsjournal.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sluz-my.sharepoint.com/personal/erion_jasiqi_sluz_ch/Documents/BBZW/3. Lehrjahr/2. Semester/IPT9.1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erion_en333sn\Documents\GitHubProjects\IPT9.1\PC4NOOBS_Frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419" documentId="8_{4B4EDC06-3713-41D7-A95F-E1F5DCA2423D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F69B5BED-10FA-40C0-91E2-EB94A0D86835}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E914930-0F26-4C7F-ACBE-63A6FB02E1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8A08529F-020D-4EF6-8B0F-8FDF88234E91}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="43">
   <si>
     <t>Datum</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>Am Arbeitsjournal gearbeitet, in Datenbank für jede Kategorie eine Tabelle erstellt, von Unity zu google 3D Viewer gewechselt</t>
+  </si>
+  <si>
+    <t>Komponentendaten vom Code zur Plesk Datenbank bewegt</t>
   </si>
 </sst>
 </file>
@@ -759,14 +762,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -804,7 +803,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -910,7 +909,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1052,7 +1051,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1077,7 +1076,7 @@
     <row r="1" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F1" s="24">
         <f>SUM(F4:F9998)</f>
-        <v>3.8194444444444442</v>
+        <v>3.8611111111111107</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>12</v>
@@ -1323,7 +1322,7 @@
         <v>1.7361111111111112E-2</v>
       </c>
       <c r="F11" s="14">
-        <f t="shared" ref="F11:F23" si="3">D11-C11-E11</f>
+        <f t="shared" ref="F11:F24" si="3">D11-C11-E11</f>
         <v>0.19097222222222215</v>
       </c>
       <c r="G11" s="20" t="s">
@@ -1660,7 +1659,7 @@
         <v>40</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>19</v>
@@ -1668,14 +1667,31 @@
       <c r="J23" s="9"/>
     </row>
     <row r="24" spans="2:10" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="19"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="7"/>
+      <c r="B24" s="19">
+        <v>46145</v>
+      </c>
+      <c r="C24" s="20">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D24" s="20">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E24" s="20">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <f t="shared" si="3"/>
+        <v>4.1666666666666741E-2</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="J24" s="9"/>
     </row>
     <row r="25" spans="2:10" ht="18" thickBot="1" x14ac:dyDescent="0.4">
@@ -15785,6 +15801,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="08a37d9d-9576-4bab-89c6-ad9e0707cb90">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8e922e2c-d434-4569-88ac-67afeec8ca9b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100FBD5B87398E0F546803C08AF34E277D4" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="8f3006300d74dcf5c8393aab099a9773">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="08a37d9d-9576-4bab-89c6-ad9e0707cb90" xmlns:ns3="8e922e2c-d434-4569-88ac-67afeec8ca9b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a6a5f73e2b0a5c19ac83c75db5db3b5" ns2:_="" ns3:_="">
     <xsd:import namespace="08a37d9d-9576-4bab-89c6-ad9e0707cb90"/>
@@ -16013,27 +16049,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFA06A0D-D48F-42AE-8105-5F765D33BA65}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="08a37d9d-9576-4bab-89c6-ad9e0707cb90"/>
+    <ds:schemaRef ds:uri="8e922e2c-d434-4569-88ac-67afeec8ca9b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="08a37d9d-9576-4bab-89c6-ad9e0707cb90">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8e922e2c-d434-4569-88ac-67afeec8ca9b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D74C8F1-41F1-4523-8F31-FF3E663963D9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D5BC23-A88D-41AB-87E5-E67415B8321A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16050,23 +16085,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D74C8F1-41F1-4523-8F31-FF3E663963D9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFA06A0D-D48F-42AE-8105-5F765D33BA65}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="08a37d9d-9576-4bab-89c6-ad9e0707cb90"/>
-    <ds:schemaRef ds:uri="8e922e2c-d434-4569-88ac-67afeec8ca9b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>